--- a/PCI-RR-friendly-journals_SNIP.xlsx
+++ b/PCI-RR-friendly-journals_SNIP.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zephyr/Documents/Uni/_projects/rr-model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3629670A-4E0F-664D-BD41-EE4F849B83FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7749DBF-2F49-E34E-B0A4-F9CC6E8CA979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{905EA813-4A13-C941-AAF5-0505B010CC59}"/>
+    <workbookView xWindow="22860" yWindow="2180" windowWidth="19280" windowHeight="17620" xr2:uid="{905EA813-4A13-C941-AAF5-0505B010CC59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>journal</t>
   </si>
@@ -44,9 +44,6 @@
     <t>SNIP</t>
   </si>
   <si>
-    <t>retrieval date</t>
-  </si>
-  <si>
     <t>Addiction Research &amp; Theory</t>
   </si>
   <si>
@@ -156,13 +153,49 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>PCI_status</t>
+  </si>
+  <si>
+    <t>retrieval_date</t>
+  </si>
+  <si>
+    <t>PCI friendly</t>
+  </si>
+  <si>
+    <t>i-Perception</t>
+  </si>
+  <si>
+    <t>Journal of Experimental Psychology: Learning, Memory, and Cognition</t>
+  </si>
+  <si>
+    <t>Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>Perception</t>
+  </si>
+  <si>
+    <t>PLOS Biology</t>
+  </si>
+  <si>
+    <t>Psychology of Addictive Behaviors</t>
+  </si>
+  <si>
+    <t>Psychonomic Bulletin &amp; Review</t>
+  </si>
+  <si>
+    <t>Sport, Exercise, and Performance Psychology</t>
+  </si>
+  <si>
+    <t>PCI interested</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -177,6 +210,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -200,10 +245,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -519,466 +566,767 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ACC5EAC-4BDF-F24A-8F46-778D12CBBA6E}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D2">
+        <v>2023</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C2">
-        <v>2023</v>
-      </c>
-      <c r="D2" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3">
+        <v>0.48</v>
+      </c>
+      <c r="D3">
+        <v>2023</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>6.4</v>
+      </c>
+      <c r="D4">
+        <v>2023</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5">
+        <v>0.43</v>
+      </c>
+      <c r="D5">
+        <v>2023</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6">
+        <v>1.67</v>
+      </c>
+      <c r="D6">
+        <v>2021</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8">
+        <v>1.23</v>
+      </c>
+      <c r="D8">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10">
+        <v>1.24</v>
+      </c>
+      <c r="D10">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>0.71</v>
+      </c>
+      <c r="D11">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>0.78</v>
+      </c>
+      <c r="D12">
+        <v>2023</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
+        <v>1.22</v>
+      </c>
+      <c r="D16">
+        <v>2023</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18">
+        <v>1.05</v>
+      </c>
+      <c r="D18">
+        <v>2023</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D20">
+        <v>2023</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22">
+        <v>0.8</v>
+      </c>
+      <c r="D22">
+        <v>2023</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>1.39</v>
+      </c>
+      <c r="D23">
+        <v>2023</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>0.71</v>
+      </c>
+      <c r="D30">
+        <v>2023</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31">
+        <v>1.05</v>
+      </c>
+      <c r="D31">
+        <v>2023</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32">
+        <v>1.26</v>
+      </c>
+      <c r="D32">
+        <v>2023</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33">
+        <v>0.82</v>
+      </c>
+      <c r="D33">
+        <v>2023</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34">
         <v>0.48</v>
       </c>
-      <c r="C3">
-        <v>2023</v>
-      </c>
-      <c r="D3" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>6.4</v>
-      </c>
-      <c r="C4">
-        <v>2023</v>
-      </c>
-      <c r="D4" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>0.43</v>
-      </c>
-      <c r="C5">
-        <v>2023</v>
-      </c>
-      <c r="D5" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>1.67</v>
-      </c>
-      <c r="C6">
-        <v>2021</v>
-      </c>
-      <c r="D6" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
+      <c r="D34">
+        <v>2023</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45578</v>
+      </c>
+      <c r="H36">
+        <f>AVERAGE(C2:C36)</f>
+        <v>1.2310526315789478</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37">
+        <v>1.06</v>
+      </c>
+      <c r="D37">
+        <v>2023</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45578</v>
+      </c>
+      <c r="H37">
+        <f>AVERAGE(C37:C44)</f>
+        <v>1.9575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
         <v>1.23</v>
       </c>
-      <c r="C8">
-        <v>2023</v>
-      </c>
-      <c r="D8" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>1.24</v>
-      </c>
-      <c r="C10">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>0.71</v>
-      </c>
-      <c r="C11">
-        <v>2023</v>
-      </c>
-      <c r="D11" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>0.78</v>
-      </c>
-      <c r="C12">
-        <v>2023</v>
-      </c>
-      <c r="D12" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>1.22</v>
-      </c>
-      <c r="C16">
-        <v>2023</v>
-      </c>
-      <c r="D16" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18">
-        <v>1.05</v>
-      </c>
-      <c r="C18">
-        <v>2023</v>
-      </c>
-      <c r="D18" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="C20">
-        <v>2023</v>
-      </c>
-      <c r="D20" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22">
-        <v>0.8</v>
-      </c>
-      <c r="C22">
-        <v>2023</v>
-      </c>
-      <c r="D22" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23">
-        <v>1.39</v>
-      </c>
-      <c r="C23">
-        <v>2023</v>
-      </c>
-      <c r="D23" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30">
-        <v>0.71</v>
-      </c>
-      <c r="C30">
-        <v>2023</v>
-      </c>
-      <c r="D30" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31">
-        <v>1.05</v>
-      </c>
-      <c r="C31">
-        <v>2023</v>
-      </c>
-      <c r="D31" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32">
-        <v>1.26</v>
-      </c>
-      <c r="C32">
-        <v>2023</v>
-      </c>
-      <c r="D32" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33">
+      <c r="D38">
+        <v>2023</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>6.19</v>
+      </c>
+      <c r="D39">
+        <v>2023</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
         <v>0.82</v>
       </c>
-      <c r="C33">
-        <v>2023</v>
-      </c>
-      <c r="D33" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34">
-        <v>0.48</v>
-      </c>
-      <c r="C34">
-        <v>2023</v>
-      </c>
-      <c r="D34" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="2">
-        <v>45520</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="2">
-        <v>45520</v>
+      <c r="D40">
+        <v>2023</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>2.12</v>
+      </c>
+      <c r="D41">
+        <v>2023</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
+        <v>1.06</v>
+      </c>
+      <c r="D42">
+        <v>2023</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D43">
+        <v>2023</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="D44">
+        <v>2023</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45578</v>
       </c>
     </row>
   </sheetData>
